--- a/jira_export_2026-09-16.xlsx
+++ b/jira_export_2026-09-16.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>24,731 €</t>
+          <t>25,176 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>7,325 €</t>
+          <t>7,771 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>240 h</t>
+          <t>248 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - API Publication</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2393,10 +2393,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>0</v>
+        <v>445.5</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>0</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="24">
@@ -3906,32 +3906,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3941,49 +3941,49 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>65.73</v>
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>29.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4025,52 +4025,52 @@
         <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O46" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>65.73</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4090,44 +4090,44 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>465.85</v>
+        <v>1890</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>93.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4162,59 +4162,59 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>920</v>
-      </c>
-      <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>465.85</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>93.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4241,37 +4241,37 @@
         <v>3</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>679.5</v>
+        <v>920</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4317,53 +4317,53 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>540</v>
+        <v>679.5</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>720</v>
+        <v>906</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4373,49 +4373,49 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>568.8</v>
+        <v>540</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4461,19 +4461,19 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>505</v>
+        <v>568.8</v>
       </c>
       <c r="P52" s="15" t="n">
         <v>0</v>
@@ -4482,27 +4482,27 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4529,23 +4529,23 @@
         <v>3</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
@@ -4554,12 +4554,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4589,69 +4589,69 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>251.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4661,69 +4661,69 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O55" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>691.9</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>251.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
@@ -4749,19 +4749,19 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="15" t="n">
-        <v>3339.2</v>
+        <v>171.4</v>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
         <v>0</v>
@@ -4770,27 +4770,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4805,12 +4805,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4821,19 +4821,19 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O57" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
@@ -4842,27 +4842,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
@@ -4893,16 +4893,16 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4914,27 +4914,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4965,16 +4965,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4986,32 +4986,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5021,38 +5021,38 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O60" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>385.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5109,53 +5109,53 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>16</v>
+        <v>625</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>337.5</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>18.29</v>
+        <v>385.71</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5165,49 +5165,49 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O62" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5242,27 +5242,27 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5309,32 +5309,32 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5346,32 +5346,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
@@ -5393,57 +5393,57 @@
         <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
-        <v>1400</v>
+        <v>500</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
-        <v>466.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5453,49 +5453,49 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="P66" s="15" t="n">
-        <v>0</v>
+        <v>466.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5530,29 +5530,29 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O67" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5562,32 +5562,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5597,32 +5597,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K68" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5634,32 +5634,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5669,34 +5669,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5706,32 +5706,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5741,28 +5741,28 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
@@ -5778,12 +5778,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5818,29 +5818,29 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5850,32 +5850,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5885,69 +5885,69 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O72" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5957,49 +5957,49 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O73" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P73" s="12" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6045,19 +6045,19 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
-        <v>823.65</v>
+        <v>590.15</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6066,12 +6066,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6117,19 +6117,19 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O75" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
+        <v>823.65</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
@@ -6138,32 +6138,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6178,27 +6178,27 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6210,12 +6210,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6250,27 +6250,27 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6282,32 +6282,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
@@ -6333,16 +6333,16 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6354,12 +6354,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6394,64 +6394,64 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
-        <v>1470</v>
+        <v>588</v>
+      </c>
+      <c r="O79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>452.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31735</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[EVREUX] - Initiation à la redevance</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE EVREUX</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Initiation à la redevance</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6461,69 +6461,69 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31739</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00158914</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>0</v>
+        <v>1470</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>0</v>
+        <v>452.31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31735</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[EVREUX] - Initiation à la redevance</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE EVREUX</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Initiation à la redevance</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6533,34 +6533,34 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31739</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00158914</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6570,12 +6570,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
@@ -6621,16 +6621,16 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6642,32 +6642,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
@@ -6693,16 +6693,16 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6714,27 +6714,27 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
@@ -6761,14 +6761,22 @@
         <v>7</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L84" s="14" t="inlineStr"/>
-      <c r="M84" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6778,12 +6786,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6793,12 +6801,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6808,7 +6816,7 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -6818,25 +6826,17 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L85" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M85" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
       <c r="N85" s="12" t="n">
         <v>0</v>
       </c>
@@ -6850,32 +6850,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6885,34 +6885,34 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6922,12 +6922,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6973,19 +6973,19 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="O87" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
         <v>0</v>
@@ -6994,12 +6994,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
@@ -7045,19 +7045,19 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O88" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>281</v>
       </c>
       <c r="P88" s="15" t="n">
         <v>0</v>
@@ -7066,12 +7066,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7117,16 +7117,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7138,12 +7138,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7178,27 +7178,27 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O90" s="16" t="n">
         <v>0</v>
@@ -7210,32 +7210,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7245,32 +7245,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7282,27 +7282,27 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
@@ -7322,29 +7322,29 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.75</v>
+        <v>3.5</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7405,18 +7405,18 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O93" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7477,16 +7477,16 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O94" s="16" t="n">
         <v>0</v>
@@ -7498,32 +7498,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7533,35 +7533,35 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O95" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
         <v>0</v>
@@ -7570,30 +7570,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7603,35 +7605,35 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P96" s="15" t="n">
         <v>0</v>
@@ -7640,12 +7642,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7655,13 +7657,11 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v/>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7680,23 +7680,23 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7979,18 +7979,18 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -8000,12 +8000,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -8015,11 +8015,13 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -8033,34 +8035,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8070,12 +8072,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8085,34 +8087,48 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F103" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H103" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8126,12 +8142,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8141,48 +8157,34 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F104" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr"/>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H104" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr"/>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M104" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
       <c r="N104" s="15" t="n">
         <v>0</v>
       </c>
@@ -8196,12 +8198,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8211,7 +8213,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8229,34 +8231,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8266,22 +8268,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8299,34 +8301,34 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8336,22 +8338,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8369,49 +8371,49 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="12" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8421,13 +8423,11 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v/>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -8436,54 +8436,54 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P108" s="15" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8493,11 +8493,13 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8506,33 +8508,33 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8548,12 +8550,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8563,7 +8565,7 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8586,23 +8588,23 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>14</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8667,12 +8669,12 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8703,7 +8705,7 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8737,12 +8739,12 @@
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
@@ -8773,7 +8775,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8807,12 +8809,12 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8828,12 +8830,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8843,7 +8845,7 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8861,28 +8863,28 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
@@ -8898,22 +8900,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8936,29 +8938,29 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8968,12 +8970,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21548</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[Evreux] AME</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8983,7 +8985,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -9006,29 +9008,29 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28039</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>477841</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9038,12 +9040,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21548</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Evreux] AME</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9053,7 +9055,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9071,28 +9073,28 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>6.5</v>
+        <v>0.25</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28039</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>477841</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
@@ -9108,22 +9110,22 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9141,28 +9143,28 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1</v>
+        <v>6.75</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9178,22 +9180,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9216,29 +9218,29 @@
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O119" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9248,12 +9250,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9263,7 +9265,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9281,34 +9283,34 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
@@ -9318,12 +9320,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9333,7 +9335,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9351,12 +9353,12 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
@@ -9367,12 +9369,12 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
@@ -9388,22 +9390,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9421,28 +9423,28 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9507,12 +9509,12 @@
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
@@ -9528,12 +9530,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9543,7 +9545,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9556,27 +9558,35 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr"/>
-      <c r="M124" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M124" s="14" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N124" s="15" t="n">
         <v>0</v>
       </c>
@@ -9590,22 +9600,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9623,7 +9633,7 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -9635,7 +9645,7 @@
         <v>21</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>5.58</v>
+        <v>6</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -9652,22 +9662,22 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9675,44 +9685,36 @@
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M126" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>7.33</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
       <c r="N126" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="15" t="n">
@@ -9722,22 +9724,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9745,7 +9747,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
@@ -9755,34 +9757,34 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O127" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9807,7 +9809,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9841,7 +9843,7 @@
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
@@ -9862,12 +9864,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9877,7 +9879,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9907,22 +9909,22 @@
         <v>21</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O129" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
@@ -9932,22 +9934,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-17710</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[Saint Lo] Migration</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>Saint Lo</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9955,32 +9957,44 @@
       </c>
       <c r="F130" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G130" s="14" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>25/11/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr"/>
-      <c r="M130" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M130" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
@@ -9990,22 +10004,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-17710</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[Saint Lo] Migration</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>Saint Lo</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10013,29 +10027,25 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G131" s="11" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr"/>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>25/11/2024</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="11" t="inlineStr"/>
       <c r="M131" s="11" t="inlineStr"/>
@@ -10052,22 +10062,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10090,14 +10100,14 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L132" s="14" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -10114,22 +10124,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10152,14 +10162,14 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L133" s="11" t="inlineStr"/>
       <c r="M133" s="11" t="inlineStr"/>
@@ -10176,22 +10186,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10209,19 +10219,19 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>3.58</v>
+        <v>0.75</v>
       </c>
       <c r="L134" s="14" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -10238,22 +10248,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10266,35 +10276,27 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M135" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10308,22 +10310,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10336,23 +10338,35 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr"/>
-      <c r="M136" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M136" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10366,12 +10380,12 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -10381,7 +10395,7 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10397,32 +10411,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H137" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H137" s="11" t="inlineStr"/>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
         <v>0</v>
       </c>
@@ -10436,28 +10438,26 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E138" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="n">
+        <v/>
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
@@ -10471,12 +10471,12 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
@@ -10485,8 +10485,16 @@
       <c r="K138" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L138" s="14" t="inlineStr"/>
-      <c r="M138" s="14" t="inlineStr"/>
+      <c r="L138" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M138" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N138" s="15" t="n">
         <v>0</v>
       </c>
@@ -10500,23 +10508,27 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
@@ -10531,19 +10543,19 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10560,21 +10572,25 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr"/>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10582,26 +10598,26 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
         <v>0</v>
@@ -10616,18 +10632,18 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr"/>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
@@ -10638,7 +10654,7 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr"/>
@@ -10651,9 +10667,13 @@
         <v>2</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="12" t="n">
         <v>0</v>
@@ -10668,18 +10688,18 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr"/>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr"/>
@@ -10690,31 +10710,23 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10728,18 +10740,18 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr"/>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr"/>
@@ -10756,23 +10768,23 @@
       <c r="H143" s="11" t="inlineStr"/>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M143" s="11" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N143" s="12" t="n">
@@ -10788,18 +10800,18 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr"/>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr"/>
@@ -10810,59 +10822,119 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K144" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr"/>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr"/>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr"/>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
           <t>04/04/2025</t>
         </is>
       </c>
-      <c r="J144" s="14" t="n">
+      <c r="J145" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="K144" s="14" t="n">
+      <c r="K145" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
-      <c r="N144" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="17" t="inlineStr">
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
+      <c r="N145" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B145" s="17" t="inlineStr"/>
-      <c r="C145" s="17" t="inlineStr"/>
-      <c r="D145" s="17" t="inlineStr"/>
-      <c r="E145" s="17" t="inlineStr"/>
-      <c r="F145" s="17" t="inlineStr"/>
-      <c r="G145" s="17" t="inlineStr"/>
-      <c r="H145" s="17" t="inlineStr"/>
-      <c r="I145" s="17" t="inlineStr"/>
-      <c r="J145" s="17" t="inlineStr"/>
-      <c r="K145" s="17" t="inlineStr"/>
-      <c r="L145" s="17" t="inlineStr"/>
-      <c r="M145" s="17" t="inlineStr"/>
-      <c r="N145" s="18" t="n">
+      <c r="B146" s="17" t="inlineStr"/>
+      <c r="C146" s="17" t="inlineStr"/>
+      <c r="D146" s="17" t="inlineStr"/>
+      <c r="E146" s="17" t="inlineStr"/>
+      <c r="F146" s="17" t="inlineStr"/>
+      <c r="G146" s="17" t="inlineStr"/>
+      <c r="H146" s="17" t="inlineStr"/>
+      <c r="I146" s="17" t="inlineStr"/>
+      <c r="J146" s="17" t="inlineStr"/>
+      <c r="K146" s="17" t="inlineStr"/>
+      <c r="L146" s="17" t="inlineStr"/>
+      <c r="M146" s="17" t="inlineStr"/>
+      <c r="N146" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O145" s="18" t="n">
-        <v>24730.768</v>
-      </c>
-      <c r="P145" s="18" t="n">
-        <v>173.16</v>
+      <c r="O146" s="18" t="n">
+        <v>25176.268</v>
+      </c>
+      <c r="P146" s="18" t="n">
+        <v>166.65</v>
       </c>
     </row>
   </sheetData>
@@ -11008,6 +11080,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12035,16 +12108,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>75.92</v>
+        <v>76.42</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>21.17</v>
+        <v>22.92</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>10.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>107.33</v>
+        <v>109.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>20.42</v>
@@ -12054,7 +12127,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12138,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>31.5</v>
+        <v>37.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -12074,7 +12147,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -12084,7 +12157,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -12181,10 +12254,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>397437</v>
+        <v>396992</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>174674</v>
+        <v>174228</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>222763</v>
@@ -12206,10 +12279,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>172587</v>
+        <v>172142</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>71361</v>
+        <v>70916</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>101226</v>
@@ -12260,7 +12333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12284,7 +12357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 19 commande(s)</t>
+          <t>Épics créées ce mois — 21 commande(s)</t>
         </is>
       </c>
     </row>
@@ -12339,22 +12412,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35733</t>
+          <t>PDMDEP-35758</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35727</t>
+          <t>PDMDEP-35752</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIEUX BOUCAU</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -12364,7 +12437,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -12374,7 +12447,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00181531</t>
+          <t>00181622</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -12466,22 +12539,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -12491,7 +12564,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -12501,32 +12574,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180931</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -12546,11 +12619,11 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00181049</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="10">
@@ -12601,22 +12674,22 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -12626,7 +12699,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -12636,7 +12709,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
@@ -12646,12 +12719,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35672</t>
+          <t>PDMDEP-35703</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35696</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -12661,7 +12734,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNE DE HARFLEUR</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -12681,7 +12754,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00181382</t>
+          <t>00181438</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -12691,22 +12764,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35703</t>
+          <t>PDMDEP-35733</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35696</t>
+          <t>PDMDEP-35727</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARFLEUR</t>
+          <t>COMMUNE DE VIEUX BOUCAU</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -12726,7 +12799,7 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00181438</t>
+          <t>00181531</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
@@ -12736,22 +12809,22 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35747</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35743</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE D'EYSINES</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -12761,7 +12834,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -12771,42 +12844,42 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00181626</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>28915.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -12816,7 +12889,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -12826,32 +12899,32 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35687</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -12861,32 +12934,32 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00181396</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>2333.33</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -12906,32 +12979,32 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>840</v>
+        <v>6382.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -12951,32 +13024,32 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>895</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -12986,7 +13059,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -12996,7 +13069,7 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
@@ -13051,22 +13124,22 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -13086,32 +13159,32 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>455</v>
+        <v>840</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -13131,32 +13204,32 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>00180506</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
-        <v>3974</v>
+        <v>895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -13166,69 +13239,117 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>0015489263</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>00181167</t>
-        </is>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>6382.5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>19 commande(s)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="n">
-        <v>52730</v>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>455</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>9 commande(s)</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="n">
-        <v>14880</v>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35439</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35435</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>00180506</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>3974</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" s="17" t="n"/>
@@ -13239,10 +13360,52 @@
       <c r="G26" s="17" t="n"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>10 commande(s)</t>
+          <t>21 commande(s)</t>
         </is>
       </c>
       <c r="I26" s="24" t="n">
+        <v>52730</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>9 commande(s)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>14880</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>12 commande(s)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="n">
         <v>37850</v>
       </c>
     </row>
@@ -13257,7 +13420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -13278,7 +13441,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2 clôture(s) : 2 projet(s), 0 rework</t>
+          <t>3 clôture(s) : 3 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -13348,59 +13511,89 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35165</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LORGUES] - Ajout d'une nouvelle régie (Caisse / c</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LORGUES</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-33699</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assist</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F7" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n">
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-09-16.xlsx
+++ b/jira_export_2026-09-16.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>248 h</t>
+          <t>258 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2377,7 +2377,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>445.5</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>356.4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24">
@@ -4673,7 +4673,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>691.9</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>251.6</v>
+        <v>212.89</v>
       </c>
     </row>
     <row r="56">
@@ -7329,7 +7329,7 @@
         <v>8</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>17</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>21</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>7.33</v>
+        <v>12.08</v>
       </c>
       <c r="L126" s="14" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
         <v>25176.268</v>
       </c>
       <c r="P146" s="18" t="n">
-        <v>166.65</v>
+        <v>158.27</v>
       </c>
     </row>
   </sheetData>
@@ -12108,16 +12108,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>76.42</v>
+        <v>79.17</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>22.92</v>
+        <v>27.67</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>10.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>109.58</v>
+        <v>117.08</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>20.42</v>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -12147,7 +12147,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>69</v>
+        <v>70.75</v>
       </c>
     </row>
   </sheetData>
@@ -13420,7 +13420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -13441,7 +13441,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 clôture(s) : 3 projet(s), 0 rework</t>
+          <t>5 clôture(s) : 5 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -13511,17 +13511,17 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LORGUES] - Ajout d'une nouvelle régie (Caisse / c</t>
+          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -13541,59 +13541,119 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-35165</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LORGUES] - Ajout d'une nouvelle régie (Caisse / c</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LORGUES</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35583</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE CHAMBERY] - GeODP - Export CSV spécifique</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-33699</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assist</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F9" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n">
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n">
         <v>0</v>
       </c>
     </row>
